--- a/daily_matches/job_matches_2026-09-05.xlsx
+++ b/daily_matches/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Sr ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Boston, AL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ad84a4ec3d68d3</t>
+          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Boston, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, TensorFlow, Redshift, BigQuery, Data Lake, CI/CD, Snowflake, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a6c188c89ec231</t>
+          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connectedx, Inc.</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dfb3631d66d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Beckett</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python</t>
+          <t>S3, Redshift, BigQuery, Kinesis, Git, BigQuery, Redshift, MongoDB, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b0c15a37577d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07187e8974fdaae2</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf90c574006fcab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy Supply Data Scientist (I&amp;II)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PacifiCorp</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Hadoop, MySQL, Tableau, Power BI, Python</t>
+          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc503ca970a43870</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI/ML Engineering, GPU ML Serving</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Cassandra, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3805ca4af5e5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2722d0a5d4347ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer - Application Development</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, SQL</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351358af38232da</t>
+          <t>https://www.indeed.com/viewjob?jk=51efb42a8e18b432</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Solutions AI Application Developer III</t>
+          <t>Senior Data Governance Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>AIT Worldwide Logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Itasca, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, FastAPI, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e2477e10d6992a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS/Databricks</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Apache Airflow, CI/CD, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc46b9f3c171738d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4d6c109f730962</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ddc19f7662ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=00995c70d4213832</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Matterport - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pie Insurance</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cf632662e11a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=905694f5820691ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Grading Operations</t>
+          <t>Sr. Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Cortex, S3, Kubernetes, GitHub Actions, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d3a613ac15910d</t>
+          <t>https://www.indeed.com/viewjob?jk=04cbe9e3f0d40946</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cybersecurity Automation Engineer III</t>
+          <t>Senior Back End Engineer, Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4e10ad83956a06</t>
+          <t>https://www.indeed.com/viewjob?jk=f079c424f1c24696</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Back End Engineer, Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fe8890ede9330b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce3ce22ae95ac6ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, Snowflake, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a11f8a5d5d8fda</t>
+          <t>https://www.indeed.com/viewjob?jk=bde18bd0b3fbb361</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Back End Engineer, Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,497 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473f31dd3827142a</t>
+          <t>https://www.indeed.com/viewjob?jk=35ac89ac03a0dd77</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Back End Engineer, Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Precision CastParts</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Gate, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7406c9cb7ad14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer-AI Enabled</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antero Resources</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e53b2cd605dcdb9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Operations</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SCAN Health Plan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Long Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44162dbb6a22ced6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Summer 2027 Industrial Engineering Intern- Bachelor's (Santa Clara, CA)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eccd33eea09afd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Security Vulnerability Engineer (R-00224)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>True Zero Technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Hugging Face, Pinecone, TensorFlow, PyTorch, Keras, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e7e1cc8bbd67322</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>University of Utah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7058848a10aff812</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8f1ff22399e8e1</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=251010d557cfd32b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c62daa33ee6fafc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af0c91feb90f9b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Database Platform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f964a02ba70daf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Database Platform</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c352b39049466b94</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Database Platform</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf3496f01d0b6cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist - Process Modeling &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SMS group GmbH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Keras, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3a2dd3a72ddaebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Summer 2027 AI Intern, Advanced Rail Technology</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Progress Rail</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>La Grange, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6065a21b3dfb91bc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-05.xlsx
+++ b/daily_matches/job_matches_2026-09-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr ML Engineer</t>
+          <t>Full Stack Architect - AI &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, S3, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1af082f7d7e8</t>
+          <t>https://www.indeed.com/viewjob?jk=caf8c9fa09debc3a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, S3, Docker, Jenkins, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=383bce16ad78ce6b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Snowflake, Redshift</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Redshift, BigQuery, Kinesis, Git, BigQuery, Redshift, MongoDB, NoSQL, Tableau</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
+          <t>https://www.indeed.com/viewjob?jk=9faddc3559ec4193</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
+          <t>Data Scientist, RAG, Copilot, S3, EC2, FastAPI, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf90c574006fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=9708a71c0bb34afc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
+          <t>Copilot, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2722d0a5d4347ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, S3, EC2, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51efb42a8e18b432</t>
+          <t>https://www.indeed.com/viewjob?jk=00a71842311f4d67</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=b97a4d718b259969</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4d6c109f730962</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cd5374a345b985</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bartlesville, OK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00995c70d4213832</t>
+          <t>https://www.indeed.com/viewjob?jk=a3ea53050afc37fb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Matterport - Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905694f5820691ce</t>
+          <t>https://www.indeed.com/viewjob?jk=336b884b76a59e38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Kubernetes, GitHub Actions, Git, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04cbe9e3f0d40946</t>
+          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer, Platform</t>
+          <t>Junior Generative AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Cleary Gottlieb Steen &amp; Hamilton LLP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Databricks, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f079c424f1c24696</t>
+          <t>https://www.indeed.com/viewjob?jk=fc90b335a764a448</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer, Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3ce22ae95ac6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e903b6f7c76342d0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, Snowflake, Kafka, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde18bd0b3fbb361</t>
+          <t>https://www.indeed.com/viewjob?jk=5d46a09b9313f862</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer, Platform</t>
+          <t>Senior Generative AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Cleary Gottlieb Steen &amp; Hamilton LLP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ac89ac03a0dd77</t>
+          <t>https://www.indeed.com/viewjob?jk=db7ec5305776eb12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer, Platform</t>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, MySQL, SQL, R, Java</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7406c9cb7ad14d</t>
+          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer-AI Enabled</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Antero Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53b2cd605dcdb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Operations</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44162dbb6a22ced6</t>
+          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Summer 2027 Industrial Engineering Intern- Bachelor's (Santa Clara, CA)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eccd33eea09afd5</t>
+          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Security Vulnerability Engineer (R-00224)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, Pinecone, TensorFlow, PyTorch, Keras, Python, R, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7e1cc8bbd67322</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7058848a10aff812</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Web Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, GitHub Actions, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251010d557cfd32b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2162b2f055aa62</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Associate IT Operations Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Atlanta, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, R, Java</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62daa33ee6fafc1</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb0f341d2bf6c86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Associate Software Engineer, AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0c91feb90f9b77</t>
+          <t>https://www.indeed.com/viewjob?jk=dea955d1336017bb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer - Database Platform</t>
+          <t>Software Engineer, IQ Platform Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+          <t>RAG, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f964a02ba70daf5</t>
+          <t>https://www.indeed.com/viewjob?jk=d79ab512a757a4dd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer - Database Platform</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c352b39049466b94</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Systems Engineer - Database Platform</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,77 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3496f01d0b6cc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist - Process Modeling &amp; Machine Learning</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SMS group GmbH</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Keras, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a2dd3a72ddaebf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Summer 2027 AI Intern, Advanced Rail Technology</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Progress Rail</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>La Grange, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Docker, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6065a21b3dfb91bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
         </is>
       </c>
     </row>
